--- a/Base de datos - Poster.xlsx
+++ b/Base de datos - Poster.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F0753DF-3A01-4B57-AE5B-B799F272C991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{0F0753DF-3A01-4B57-AE5B-B799F272C991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{232EB09E-3C11-4124-BF86-1B0380386B2D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3936" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="356">
   <si>
     <t>Fecha</t>
   </si>
@@ -1059,9 +1059,6 @@
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República viernes, 16 de octubre de 2026 9:45:24 a. m.</t>
-  </si>
-  <si>
     <t>Nombre de la serie</t>
   </si>
   <si>
@@ -1084,6 +1081,9 @@
   </si>
   <si>
     <t>De acuerdo con lo establecido en el artículo 152 de la Ley 488 de 1998, en el artículo 16 de la Ley 0141 de 1994, modificado por el artículo 16 (parágrafo 9o.) de la Ley 756 de 2002, y en la Resolución número 000476 del 30 de junio de 2026 de la Unidad de Planeación Minero-Energética del Ministerio de Minas y Energía, se certifican los precios por gramo para efectos de la liquidación de las rentas originadas en la explotación de los siguientes metales, así:</t>
+  </si>
+  <si>
+    <t>Precio</t>
   </si>
 </sst>
 </file>
@@ -3365,7 +3365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B345"/>
+  <dimension ref="A1:B344"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" customWidth="1"/>
@@ -3377,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -6116,11 +6116,6 @@
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>346</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A345" t="s">
-        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -6144,19 +6139,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -6167,13 +6162,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -6184,13 +6179,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -6201,13 +6196,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>355</v>
       </c>
     </row>
   </sheetData>
